--- a/public/template.xlsx
+++ b/public/template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://denpa.sharepoint.com/sites/a_1B/Shared Documents/41_卒業研究(担任)/03_週報/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="8_{00F7764F-F9AE-4CFC-B8EB-A7BEE9E81AB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E16A7B47-F63C-4005-8695-DB1581F678B7}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="8_{00F7764F-F9AE-4CFC-B8EB-A7BEE9E81AB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A6279E7-65EA-4439-BD2D-EE55DF61B8AA}"/>
   <bookViews>
-    <workbookView xWindow="-336" yWindow="1236" windowWidth="17724" windowHeight="10620" activeTab="1" xr2:uid="{20E13645-532A-45F3-A56F-5B13C3EF8341}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{20E13645-532A-45F3-A56F-5B13C3EF8341}"/>
   </bookViews>
   <sheets>
     <sheet name="ひな形（このシートをコピー）" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="18">
   <si>
     <t>週初め</t>
     <rPh sb="0" eb="2">
@@ -168,20 +168,58 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t xml:space="preserve">
-【来週やること】
-○○する。
-【今週の一番困ってること】
-▲▲がわからない。</t>
+    <t>「◇◇作業を担当」</t>
+  </si>
+  <si>
+    <t>進捗報告</t>
+    <rPh sb="0" eb="4">
+      <t>シンチョクホウコク</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>「◇◇作業を担当」</t>
-    <rPh sb="3" eb="5">
+    <t>AA作業：問題BBあり。進捗50%で停滞中。
+CC作業：問題DDをEEの方法で解決。完了。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">【来週やること】
+○○する。
+【今週の一番困ってること】
+AA作業で○○がわからず停滞中。
+</t>
+    <rPh sb="31" eb="33">
       <t>サギョウ</t>
     </rPh>
-    <rPh sb="6" eb="8">
-      <t>タントウ</t>
+    <rPh sb="41" eb="44">
+      <t>テイタイチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【新規タスク】
+・DD作業。
+【継続タスク】
+・AA作業
+【完了タスク】
+・BB作業</t>
+    <rPh sb="1" eb="3">
+      <t>シンキ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>サギョウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ケイゾク</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>サギョウ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>サギョウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -296,7 +334,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -330,11 +368,20 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -879,7 +926,9 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="126" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B8" s="8"/>
+      <c r="B8" s="11" t="s">
+        <v>17</v>
+      </c>
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
@@ -893,15 +942,15 @@
       </c>
     </row>
     <row r="11" spans="1:8" ht="126" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B11" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="10"/>
+      <c r="B11" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="15"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A14" s="4" t="s">
@@ -916,13 +965,13 @@
         <v>10</v>
       </c>
       <c r="D15" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="12" t="s">
         <v>12</v>
       </c>
       <c r="E16" s="7"/>
@@ -934,7 +983,7 @@
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
       <c r="D17" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E17" s="7"/>
       <c r="F17" s="7"/>
@@ -944,7 +993,9 @@
     <row r="18" spans="2:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
-      <c r="D18" s="7"/>
+      <c r="D18" s="12" t="s">
+        <v>15</v>
+      </c>
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
       <c r="G18" s="7"/>
@@ -1691,16 +1742,16 @@
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D81EC209-85C6-4979-9FCE-8CC962161D66}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="9fe8a4a3-6c64-4b86-8618-7d8b382ab842"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="9fe8a4a3-6c64-4b86-8618-7d8b382ab842"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="364aa304-3828-4773-a036-d0e31fc55b11"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/public/template.xlsx
+++ b/public/template.xlsx
@@ -1,21 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://denpa.sharepoint.com/sites/a_1B/Shared Documents/41_卒業研究(担任)/03_週報/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Projects\weekly-report-generator\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="34" documentId="8_{00F7764F-F9AE-4CFC-B8EB-A7BEE9E81AB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A6279E7-65EA-4439-BD2D-EE55DF61B8AA}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{385C9AAE-D956-4425-8D38-0749CE91AA61}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{20E13645-532A-45F3-A56F-5B13C3EF8341}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11265" xr2:uid="{20E13645-532A-45F3-A56F-5B13C3EF8341}"/>
   </bookViews>
   <sheets>
-    <sheet name="ひな形（このシートをコピー）" sheetId="1" r:id="rId1"/>
-    <sheet name="0420週" sheetId="3" r:id="rId2"/>
-    <sheet name="0427週" sheetId="4" r:id="rId3"/>
+    <sheet name="ひな形（このシートをコピー）" sheetId="3" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -27,10 +25,10 @@
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -41,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
   <si>
     <t>週初め</t>
     <rPh sb="0" eb="2">
@@ -131,16 +129,6 @@
     <t>氏名</t>
     <rPh sb="0" eb="2">
       <t>シメイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>進捗報告（何をやったか）</t>
-    <rPh sb="0" eb="4">
-      <t>シンチョクホウコク</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ナニ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -334,7 +322,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -359,9 +347,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -371,17 +356,17 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -716,17 +701,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9F0939C-E5E8-4B6A-9875-C4F8AFD46CB7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6903BED4-FE00-4ACA-9386-6978FCBAD88F}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H21"/>
-  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
       <c r="F1" t="s">
         <v>0</v>
       </c>
@@ -737,7 +722,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
       <c r="B2" s="5"/>
       <c r="C2" t="s">
         <v>3</v>
@@ -755,45 +740,49 @@
         <v>46136</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
       <c r="B7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="126" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B8" s="8"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="10"/>
+    <row r="8" spans="1:8" ht="126" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B8" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="9"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
       <c r="B10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="126" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B11" s="8"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="10"/>
+    <row r="11" spans="1:8" ht="126" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B11" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="13"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A14" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
       <c r="B15" t="s">
         <v>9</v>
       </c>
@@ -801,37 +790,43 @@
         <v>10</v>
       </c>
       <c r="D15" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
-      <c r="D16" s="7"/>
+      <c r="D16" s="14" t="s">
+        <v>11</v>
+      </c>
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
     </row>
-    <row r="17" spans="2:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
-      <c r="D17" s="7"/>
+      <c r="D17" s="7" t="s">
+        <v>12</v>
+      </c>
       <c r="E17" s="7"/>
       <c r="F17" s="7"/>
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
     </row>
-    <row r="18" spans="2:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
-      <c r="D18" s="7"/>
+      <c r="D18" s="14" t="s">
+        <v>14</v>
+      </c>
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
       <c r="G18" s="7"/>
       <c r="H18" s="7"/>
     </row>
-    <row r="19" spans="2:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
       <c r="D19" s="7"/>
@@ -840,7 +835,7 @@
       <c r="G19" s="7"/>
       <c r="H19" s="7"/>
     </row>
-    <row r="20" spans="2:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
       <c r="D20" s="7"/>
@@ -849,337 +844,7 @@
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
     </row>
-    <row r="21" spans="2:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-    </row>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="D21:H21"/>
-    <mergeCell ref="B11:H11"/>
-    <mergeCell ref="B8:H8"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="D18:H18"/>
-    <mergeCell ref="D19:H19"/>
-  </mergeCells>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="84" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6903BED4-FE00-4ACA-9386-6978FCBAD88F}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:H21"/>
-  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="18" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="F1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B2" s="5"/>
-      <c r="C2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="1">
-        <v>46132</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2" s="6">
-        <v>46136</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A5" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="126" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B8" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="10"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="126" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B11" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="15"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A14" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B15" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" t="s">
-        <v>10</v>
-      </c>
-      <c r="D15" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-    </row>
-    <row r="17" spans="2:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-    </row>
-    <row r="18" spans="2:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-    </row>
-    <row r="19" spans="2:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-    </row>
-    <row r="20" spans="2:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-    </row>
-    <row r="21" spans="2:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-    </row>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="D21:H21"/>
-    <mergeCell ref="B8:H8"/>
-    <mergeCell ref="B11:H11"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="D18:H18"/>
-    <mergeCell ref="D19:H19"/>
-  </mergeCells>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="84" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37C0F204-BBE5-4CC4-B333-07CC44C7A4C2}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:H21"/>
-  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="18" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="F1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B2" s="5"/>
-      <c r="C2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="1">
-        <v>46139</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2" s="6">
-        <v>46143</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A5" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="126" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B8" s="8"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="10"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="126" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B11" s="8"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="10"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A14" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B15" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" t="s">
-        <v>10</v>
-      </c>
-      <c r="D15" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-    </row>
-    <row r="17" spans="2:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-    </row>
-    <row r="18" spans="2:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-    </row>
-    <row r="19" spans="2:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-    </row>
-    <row r="20" spans="2:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-    </row>
-    <row r="21" spans="2:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
       <c r="D21" s="7"/>
@@ -1206,12 +871,60 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <DefaultSectionNames xmlns="9fe8a4a3-6c64-4b86-8618-7d8b382ab842" xsi:nil="true"/>
+    <AppVersion xmlns="9fe8a4a3-6c64-4b86-8618-7d8b382ab842" xsi:nil="true"/>
+    <Invited_Teachers xmlns="9fe8a4a3-6c64-4b86-8618-7d8b382ab842" xsi:nil="true"/>
+    <NotebookType xmlns="9fe8a4a3-6c64-4b86-8618-7d8b382ab842" xsi:nil="true"/>
+    <FolderType xmlns="9fe8a4a3-6c64-4b86-8618-7d8b382ab842" xsi:nil="true"/>
+    <TeamsChannelId xmlns="9fe8a4a3-6c64-4b86-8618-7d8b382ab842" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9fe8a4a3-6c64-4b86-8618-7d8b382ab842">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Invited_Students xmlns="9fe8a4a3-6c64-4b86-8618-7d8b382ab842" xsi:nil="true"/>
+    <IsNotebookLocked xmlns="9fe8a4a3-6c64-4b86-8618-7d8b382ab842" xsi:nil="true"/>
+    <CultureName xmlns="9fe8a4a3-6c64-4b86-8618-7d8b382ab842" xsi:nil="true"/>
+    <Self_Registration_Enabled xmlns="9fe8a4a3-6c64-4b86-8618-7d8b382ab842" xsi:nil="true"/>
+    <Teams_Channel_Section_Location xmlns="9fe8a4a3-6c64-4b86-8618-7d8b382ab842" xsi:nil="true"/>
+    <Teachers xmlns="9fe8a4a3-6c64-4b86-8618-7d8b382ab842">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Teachers>
+    <Students xmlns="9fe8a4a3-6c64-4b86-8618-7d8b382ab842">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Students>
+    <Student_Groups xmlns="9fe8a4a3-6c64-4b86-8618-7d8b382ab842">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Student_Groups>
+    <TaxCatchAll xmlns="364aa304-3828-4773-a036-d0e31fc55b11" xsi:nil="true"/>
+    <Templates xmlns="9fe8a4a3-6c64-4b86-8618-7d8b382ab842" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="9fe8a4a3-6c64-4b86-8618-7d8b382ab842" xsi:nil="true"/>
+    <Is_Collaboration_Space_Locked xmlns="9fe8a4a3-6c64-4b86-8618-7d8b382ab842" xsi:nil="true"/>
+    <LMS_Mappings xmlns="9fe8a4a3-6c64-4b86-8618-7d8b382ab842" xsi:nil="true"/>
+    <Owner xmlns="9fe8a4a3-6c64-4b86-8618-7d8b382ab842">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Owner>
+    <Distribution_Groups xmlns="9fe8a4a3-6c64-4b86-8618-7d8b382ab842" xsi:nil="true"/>
+    <Math_Settings xmlns="9fe8a4a3-6c64-4b86-8618-7d8b382ab842" xsi:nil="true"/>
+    <Has_Teacher_Only_SectionGroup xmlns="9fe8a4a3-6c64-4b86-8618-7d8b382ab842" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1656,66 +1369,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <DefaultSectionNames xmlns="9fe8a4a3-6c64-4b86-8618-7d8b382ab842" xsi:nil="true"/>
-    <AppVersion xmlns="9fe8a4a3-6c64-4b86-8618-7d8b382ab842" xsi:nil="true"/>
-    <Invited_Teachers xmlns="9fe8a4a3-6c64-4b86-8618-7d8b382ab842" xsi:nil="true"/>
-    <NotebookType xmlns="9fe8a4a3-6c64-4b86-8618-7d8b382ab842" xsi:nil="true"/>
-    <FolderType xmlns="9fe8a4a3-6c64-4b86-8618-7d8b382ab842" xsi:nil="true"/>
-    <TeamsChannelId xmlns="9fe8a4a3-6c64-4b86-8618-7d8b382ab842" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9fe8a4a3-6c64-4b86-8618-7d8b382ab842">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Invited_Students xmlns="9fe8a4a3-6c64-4b86-8618-7d8b382ab842" xsi:nil="true"/>
-    <IsNotebookLocked xmlns="9fe8a4a3-6c64-4b86-8618-7d8b382ab842" xsi:nil="true"/>
-    <CultureName xmlns="9fe8a4a3-6c64-4b86-8618-7d8b382ab842" xsi:nil="true"/>
-    <Self_Registration_Enabled xmlns="9fe8a4a3-6c64-4b86-8618-7d8b382ab842" xsi:nil="true"/>
-    <Teams_Channel_Section_Location xmlns="9fe8a4a3-6c64-4b86-8618-7d8b382ab842" xsi:nil="true"/>
-    <Teachers xmlns="9fe8a4a3-6c64-4b86-8618-7d8b382ab842">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Teachers>
-    <Students xmlns="9fe8a4a3-6c64-4b86-8618-7d8b382ab842">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Students>
-    <Student_Groups xmlns="9fe8a4a3-6c64-4b86-8618-7d8b382ab842">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Student_Groups>
-    <TaxCatchAll xmlns="364aa304-3828-4773-a036-d0e31fc55b11" xsi:nil="true"/>
-    <Templates xmlns="9fe8a4a3-6c64-4b86-8618-7d8b382ab842" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="9fe8a4a3-6c64-4b86-8618-7d8b382ab842" xsi:nil="true"/>
-    <Is_Collaboration_Space_Locked xmlns="9fe8a4a3-6c64-4b86-8618-7d8b382ab842" xsi:nil="true"/>
-    <LMS_Mappings xmlns="9fe8a4a3-6c64-4b86-8618-7d8b382ab842" xsi:nil="true"/>
-    <Owner xmlns="9fe8a4a3-6c64-4b86-8618-7d8b382ab842">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Owner>
-    <Distribution_Groups xmlns="9fe8a4a3-6c64-4b86-8618-7d8b382ab842" xsi:nil="true"/>
-    <Math_Settings xmlns="9fe8a4a3-6c64-4b86-8618-7d8b382ab842" xsi:nil="true"/>
-    <Has_Teacher_Only_SectionGroup xmlns="9fe8a4a3-6c64-4b86-8618-7d8b382ab842" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA4BAB14-B698-4FEB-869E-AD838666B255}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D81EC209-85C6-4979-9FCE-8CC962161D66}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="9fe8a4a3-6c64-4b86-8618-7d8b382ab842"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="364aa304-3828-4773-a036-d0e31fc55b11"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1740,18 +1414,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D81EC209-85C6-4979-9FCE-8CC962161D66}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA4BAB14-B698-4FEB-869E-AD838666B255}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="9fe8a4a3-6c64-4b86-8618-7d8b382ab842"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="364aa304-3828-4773-a036-d0e31fc55b11"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>